--- a/countries/br-ac/2000-2004.xlsx
+++ b/countries/br-ac/2000-2004.xlsx
@@ -773,6 +773,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -909,6 +914,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1045,6 +1055,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1181,6 +1196,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1317,6 +1337,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1838,6 +1863,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1974,6 +2004,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2110,6 +2145,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2246,6 +2286,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2382,6 +2427,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2903,6 +2953,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3039,6 +3094,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3175,6 +3235,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3311,6 +3376,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3447,6 +3517,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3583,6 +3658,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3719,6 +3799,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3855,6 +3940,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3991,6 +4081,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4127,6 +4222,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4263,6 +4363,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4399,6 +4504,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4535,6 +4645,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4671,6 +4786,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4807,6 +4927,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5328,6 +5453,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5464,6 +5594,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5600,6 +5735,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5736,6 +5876,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5872,6 +6017,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6393,6 +6543,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6529,6 +6684,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6665,6 +6825,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6801,6 +6966,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6937,6 +7107,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO44" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7458,6 +7633,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO47" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7594,6 +7774,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO48" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7730,6 +7915,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO49" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7866,6 +8056,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO50" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8002,6 +8197,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO51" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8138,6 +8338,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8274,6 +8479,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO53" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8410,6 +8620,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO54" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8546,6 +8761,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO55" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8682,6 +8902,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO56" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8818,6 +9043,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO57" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8954,6 +9184,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO58" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9090,6 +9325,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO59" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9226,6 +9466,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO60" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9362,6 +9607,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO61" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9498,6 +9748,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO62" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9634,6 +9889,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO63" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9770,6 +10030,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO64" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9906,6 +10171,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO65" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10042,6 +10312,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO66" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10178,6 +10453,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO67" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10314,6 +10594,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO68" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10450,6 +10735,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO69" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10971,6 +11261,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO72" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11107,6 +11402,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO73" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11243,6 +11543,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO74" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11379,6 +11684,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO75" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11515,6 +11825,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO76" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11651,6 +11966,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO77" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11787,6 +12107,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO78" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11923,6 +12248,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO79" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12059,6 +12389,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO80" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12195,6 +12530,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO81" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12331,6 +12671,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO82" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12467,6 +12812,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO83" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12603,6 +12953,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO84" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12739,6 +13094,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO85" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13260,6 +13620,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO88" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13396,6 +13761,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO89" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13532,6 +13902,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO90" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13668,6 +14043,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO91" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13804,6 +14184,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO92" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13940,6 +14325,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO93" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14076,6 +14466,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO94" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14212,6 +14607,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO95" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14348,6 +14748,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO96" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14484,6 +14889,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO97" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14620,6 +15030,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO98" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14756,6 +15171,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO99" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14892,6 +15312,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO100" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15028,6 +15453,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO101" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15164,6 +15594,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO102" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15300,6 +15735,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO103" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15821,6 +16261,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO106" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15957,6 +16402,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO107" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16093,6 +16543,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO108" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16229,6 +16684,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO109" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16365,6 +16825,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO110" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16501,6 +16966,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO111" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16637,6 +17107,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO112" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16773,6 +17248,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO113" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16909,6 +17389,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO114" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17045,6 +17530,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO115" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17181,6 +17671,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO116" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17317,6 +17812,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO117" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17453,6 +17953,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO118" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17589,6 +18094,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO119" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17725,6 +18235,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO120" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17861,6 +18376,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO121" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18382,6 +18902,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO124" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18518,6 +19043,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO125" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18654,6 +19184,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO126" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18790,6 +19325,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO127" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18926,6 +19466,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO128" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19062,6 +19607,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO129" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19198,6 +19748,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO130" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19334,6 +19889,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO131" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19855,6 +20415,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO134" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19991,6 +20556,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO135" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20127,6 +20697,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO136" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20263,6 +20838,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO137" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20399,6 +20979,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO138" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20535,6 +21120,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO139" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20671,6 +21261,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO140" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20807,6 +21402,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO141" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20943,6 +21543,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO142" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21079,6 +21684,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO143" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21215,6 +21825,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO144" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21351,6 +21966,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO145" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21487,6 +22107,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO146" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21623,6 +22248,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO147" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21759,6 +22389,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO148" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21895,6 +22530,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO149" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22031,6 +22671,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO150" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22167,6 +22812,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO151" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22303,6 +22953,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO152" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22439,6 +23094,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO153" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22575,6 +23235,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO154" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22711,6 +23376,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO155" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22847,6 +23517,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO156" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22983,6 +23658,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO157" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23504,6 +24184,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO160" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23640,6 +24325,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO161" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23776,6 +24466,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO162" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23912,6 +24607,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO163" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24048,6 +24748,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO164" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24184,6 +24889,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO165" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24320,6 +25030,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO166" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24456,6 +25171,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO167" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24592,6 +25312,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO168" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24728,6 +25453,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO169" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24864,6 +25594,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO170" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25000,6 +25735,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO171" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25136,6 +25876,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO172" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25272,6 +26017,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO173" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25408,6 +26158,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA174" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO174" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25544,6 +26299,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA175" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO175" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25680,6 +26440,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA176" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO176" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25816,6 +26581,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA177" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO177" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25952,6 +26722,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA178" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO178" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26088,6 +26863,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA179" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO179" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26224,6 +27004,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA180" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO180" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26360,6 +27145,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA181" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO181" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26496,6 +27286,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA182" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO182" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26632,6 +27427,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA183" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO183" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27153,6 +27953,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA186" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO186" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27289,6 +28094,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA187" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO187" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27425,6 +28235,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA188" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO188" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27561,6 +28376,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA189" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO189" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27697,6 +28517,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA190" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO190" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27833,6 +28658,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA191" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO191" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27969,6 +28799,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA192" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO192" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28105,6 +28940,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA193" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO193" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28626,6 +29466,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA196" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO196" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28762,6 +29607,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA197" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO197" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28898,6 +29748,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA198" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO198" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29034,6 +29889,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA199" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO199" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29170,6 +30030,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA200" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO200" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29306,6 +30171,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA201" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO201" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29442,6 +30312,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA202" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO202" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29578,6 +30453,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA203" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO203" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29714,6 +30594,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA204" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO204" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29850,6 +30735,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA205" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO205" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29986,6 +30876,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA206" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO206" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30122,6 +31017,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA207" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO207" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30258,6 +31158,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA208" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO208" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30394,6 +31299,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA209" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO209" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30530,6 +31440,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA210" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO210" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30666,6 +31581,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA211" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO211" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30802,6 +31722,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA212" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO212" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30938,6 +31863,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA213" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO213" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31074,6 +32004,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA214" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO214" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31210,6 +32145,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA215" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO215" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31346,6 +32286,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA216" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO216" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31482,6 +32427,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA217" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO217" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31618,6 +32568,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA218" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO218" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31754,6 +32709,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA219" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO219" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31890,6 +32850,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA220" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO220" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32026,6 +32991,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA221" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO221" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32162,6 +33132,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA222" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO222" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32298,6 +33273,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA223" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO223" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32434,6 +33414,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA224" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO224" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32570,6 +33555,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA225" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO225" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32706,6 +33696,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA226" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO226" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32842,6 +33837,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA227" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO227" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33363,6 +34363,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA230" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO230" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33499,6 +34504,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA231" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO231" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33635,6 +34645,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA232" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO232" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33771,6 +34786,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA233" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO233" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33907,6 +34927,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA234" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO234" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34043,6 +35068,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA235" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO235" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34179,6 +35209,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA236" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO236" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34315,6 +35350,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA237" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO237" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34451,6 +35491,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA238" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO238" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34587,6 +35632,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA239" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO239" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34723,6 +35773,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA240" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO240" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34859,6 +35914,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA241" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO241" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34995,6 +36055,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA242" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO242" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35131,6 +36196,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA243" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO243" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35267,6 +36337,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA244" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO244" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35403,6 +36478,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA245" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO245" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35539,6 +36619,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA246" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO246" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35675,6 +36760,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA247" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO247" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35811,6 +36901,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA248" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO248" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35947,6 +37042,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA249" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO249" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36083,6 +37183,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA250" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO250" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36219,6 +37324,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA251" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO251" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36355,6 +37465,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA252" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO252" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36491,6 +37606,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA253" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO253" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36627,6 +37747,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA254" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO254" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36763,6 +37888,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA255" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO255" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36899,6 +38029,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA256" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO256" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37035,6 +38170,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA257" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO257" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37171,6 +38311,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA258" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO258" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37307,6 +38452,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA259" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO259" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37443,6 +38593,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA260" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO260" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37579,6 +38734,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA261" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO261" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37715,6 +38875,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA262" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO262" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37851,6 +39016,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA263" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO263" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37987,6 +39157,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA264" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO264" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38123,6 +39298,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA265" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO265" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38259,6 +39439,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA266" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO266" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38395,6 +39580,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA267" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO267" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38531,6 +39721,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA268" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO268" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38667,6 +39862,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA269" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO269" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38803,6 +40003,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA270" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO270" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38939,6 +40144,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA271" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO271" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39075,6 +40285,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA272" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO272" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39211,6 +40426,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA273" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO273" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39347,6 +40567,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA274" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO274" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39483,6 +40708,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA275" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO275" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39619,6 +40849,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA276" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO276" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39755,6 +40990,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA277" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO277" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39891,6 +41131,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA278" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO278" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40027,6 +41272,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA279" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO279" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40163,6 +41413,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA280" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO280" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40299,6 +41554,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA281" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO281" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40435,6 +41695,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA282" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO282" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40571,6 +41836,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA283" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO283" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40707,6 +41977,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA284" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO284" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40843,6 +42118,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA285" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO285" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41364,6 +42644,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA288" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO288" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41500,6 +42785,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA289" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO289" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41636,6 +42926,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA290" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO290" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41772,6 +43067,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA291" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO291" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41908,6 +43208,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA292" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO292" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42044,6 +43349,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA293" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO293" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42180,6 +43490,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA294" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO294" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42316,6 +43631,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA295" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO295" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42452,6 +43772,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA296" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO296" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42588,6 +43913,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA297" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO297" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42724,6 +44054,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA298" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO298" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42860,6 +44195,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA299" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO299" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42996,6 +44336,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA300" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO300" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43132,6 +44477,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA301" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO301" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43268,6 +44618,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA302" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO302" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43404,6 +44759,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA303" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO303" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43540,6 +44900,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA304" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO304" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43676,6 +45041,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA305" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO305" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43812,6 +45182,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA306" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO306" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43948,6 +45323,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA307" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO307" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44084,6 +45464,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA308" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO308" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44220,6 +45605,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA309" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO309" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44356,6 +45746,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA310" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO310" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44492,6 +45887,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA311" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO311" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44628,6 +46028,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA312" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO312" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44764,6 +46169,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA313" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO313" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44900,6 +46310,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA314" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO314" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45036,6 +46451,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA315" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO315" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45172,6 +46592,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA316" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO316" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45308,6 +46733,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA317" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO317" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45444,6 +46874,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA318" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO318" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45580,6 +47015,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA319" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO319" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45716,6 +47156,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA320" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO320" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45852,6 +47297,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA321" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO321" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45988,6 +47438,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA322" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO322" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46124,6 +47579,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA323" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO323" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46260,6 +47720,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA324" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO324" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46396,6 +47861,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA325" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO325" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46532,6 +48002,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA326" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO326" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46668,6 +48143,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA327" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO327" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46804,6 +48284,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA328" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO328" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46940,6 +48425,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA329" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO329" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -47076,6 +48566,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA330" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO330" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -47212,6 +48707,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA331" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO331" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -47348,6 +48848,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA332" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO332" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -47484,6 +48989,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA333" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO333" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -47620,6 +49130,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA334" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO334" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -47756,6 +49271,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA335" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO335" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -48277,6 +49797,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA338" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO338" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -48413,6 +49938,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA339" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO339" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -48549,6 +50079,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA340" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO340" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -48685,6 +50220,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA341" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO341" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -48821,6 +50361,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA342" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO342" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -48957,6 +50502,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA343" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO343" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49093,6 +50643,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA344" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO344" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49229,6 +50784,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA345" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO345" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49365,6 +50925,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA346" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO346" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49501,6 +51066,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA347" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO347" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49637,6 +51207,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA348" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO348" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49773,6 +51348,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA349" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO349" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49909,6 +51489,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA350" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO350" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50045,6 +51630,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA351" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO351" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50181,6 +51771,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA352" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO352" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50317,6 +51912,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA353" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO353" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50453,6 +52053,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA354" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO354" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50589,6 +52194,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA355" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO355" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50725,6 +52335,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA356" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO356" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50861,6 +52476,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA357" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO357" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50997,6 +52617,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA358" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO358" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -51133,6 +52758,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA359" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO359" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -51269,6 +52899,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA360" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO360" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -51405,6 +53040,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA361" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO361" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -51541,6 +53181,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA362" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO362" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -51677,6 +53322,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA363" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO363" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -51813,6 +53463,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA364" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO364" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -51949,6 +53604,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA365" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO365" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -52085,6 +53745,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA366" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO366" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -52221,6 +53886,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA367" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO367" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -52357,6 +54027,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA368" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO368" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -52493,6 +54168,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA369" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO369" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -53014,6 +54694,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA372" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO372" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -53150,6 +54835,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA373" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO373" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -53286,6 +54976,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA374" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO374" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -53422,6 +55117,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA375" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO375" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -53558,6 +55258,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA376" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO376" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -53694,6 +55399,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA377" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO377" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -53830,6 +55540,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA378" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO378" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -53966,6 +55681,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA379" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO379" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -54102,6 +55822,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA380" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO380" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -54238,6 +55963,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA381" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO381" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -54374,6 +56104,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA382" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO382" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -54510,6 +56245,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA383" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO383" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -54646,6 +56386,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA384" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO384" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -54782,6 +56527,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA385" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO385" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -54918,6 +56668,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA386" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO386" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -55054,6 +56809,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA387" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO387" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -55190,6 +56950,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA388" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO388" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -55326,6 +57091,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA389" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO389" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -55462,6 +57232,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA390" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO390" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -55598,6 +57373,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA391" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO391" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -55734,6 +57514,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA392" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO392" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -55870,6 +57655,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA393" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO393" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -56006,6 +57796,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA394" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO394" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -56142,6 +57937,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA395" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO395" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -56278,6 +58078,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA396" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO396" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -56414,6 +58219,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA397" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO397" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -56550,6 +58360,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA398" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO398" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -56686,6 +58501,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA399" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO399" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -56822,6 +58642,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA400" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO400" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -56958,6 +58783,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA401" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO401" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -57094,6 +58924,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA402" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO402" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -57230,6 +59065,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA403" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO403" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -57366,6 +59206,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA404" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO404" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -57502,6 +59347,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA405" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO405" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -58023,6 +59873,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA408" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO408" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -58159,6 +60014,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA409" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO409" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -58295,6 +60155,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA410" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO410" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -58431,6 +60296,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA411" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO411" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -58567,6 +60437,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA412" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO412" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -58703,6 +60578,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA413" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO413" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -58839,6 +60719,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA414" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO414" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -58975,6 +60860,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA415" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO415" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -59111,6 +61001,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA416" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO416" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -59632,6 +61527,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA419" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO419" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -59768,6 +61668,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA420" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO420" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -59904,6 +61809,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA421" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO421" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -60040,6 +61950,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA422" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO422" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -60176,6 +62091,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA423" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO423" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -60312,6 +62232,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA424" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO424" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -60448,6 +62373,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA425" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO425" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -60584,6 +62514,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA426" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO426" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -60720,6 +62655,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA427" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO427" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -61241,6 +63181,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA430" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO430" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -61377,6 +63322,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA431" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO431" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -61513,6 +63463,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA432" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO432" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -61649,6 +63604,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA433" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO433" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -61785,6 +63745,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA434" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO434" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -61921,6 +63886,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA435" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO435" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -62057,6 +64027,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA436" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO436" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -62193,6 +64168,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA437" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO437" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -62329,6 +64309,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA438" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO438" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -62850,6 +64835,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA441" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO441" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -62986,6 +64976,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA442" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO442" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -63122,6 +65117,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA443" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO443" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -63258,6 +65258,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA444" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO444" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -63394,6 +65399,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA445" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO445" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -63530,6 +65540,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA446" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO446" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -63666,6 +65681,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA447" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO447" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -63802,6 +65822,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA448" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO448" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -63938,6 +65963,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA449" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO449" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -64074,6 +66104,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA450" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO450" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -64210,6 +66245,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA451" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO451" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -64346,6 +66386,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA452" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO452" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -64482,6 +66527,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA453" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO453" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -64618,6 +66668,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA454" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO454" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -64754,6 +66809,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA455" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO455" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -64890,6 +66950,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA456" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO456" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -65026,6 +67091,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA457" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO457" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -65162,6 +67232,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA458" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO458" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -65683,6 +67758,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA461" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO461" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -65819,6 +67899,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA462" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO462" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -65955,6 +68040,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA463" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO463" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -66091,6 +68181,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA464" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO464" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -66227,6 +68322,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA465" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO465" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -66363,6 +68463,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA466" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO466" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -66499,6 +68604,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA467" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO467" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -66635,6 +68745,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA468" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO468" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -66771,6 +68886,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA469" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO469" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -66907,6 +69027,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA470" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO470" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -67043,6 +69168,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA471" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO471" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -67179,6 +69309,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA472" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO472" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -67315,6 +69450,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA473" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO473" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -67451,6 +69591,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA474" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO474" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -67587,6 +69732,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA475" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO475" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -67723,6 +69873,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA476" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO476" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -67859,6 +70014,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA477" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO477" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -67995,6 +70155,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA478" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO478" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -68516,6 +70681,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA481" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO481" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -68652,6 +70822,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA482" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO482" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -68788,6 +70963,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA483" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO483" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -68924,6 +71104,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA484" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO484" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -69060,6 +71245,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA485" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO485" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -69196,6 +71386,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA486" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO486" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -69332,6 +71527,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA487" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO487" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -69468,6 +71668,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA488" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO488" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -69604,6 +71809,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA489" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO489" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -69740,6 +71950,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA490" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO490" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -69876,6 +72091,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA491" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO491" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -70012,6 +72232,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA492" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO492" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -70148,6 +72373,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA493" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO493" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -70284,6 +72514,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA494" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO494" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -70420,6 +72655,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA495" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO495" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -70556,6 +72796,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA496" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO496" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -70692,6 +72937,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA497" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO497" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -70828,6 +73078,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA498" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO498" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -71349,6 +73604,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA501" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO501" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -71485,6 +73745,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA502" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO502" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -71621,6 +73886,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA503" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO503" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -71757,6 +74027,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA504" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO504" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -71893,6 +74168,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA505" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO505" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -72029,6 +74309,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA506" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO506" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -72165,6 +74450,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA507" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO507" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -72301,6 +74591,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA508" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO508" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -72435,6 +74730,11 @@
       <c r="S509" t="inlineStr">
         <is>
           <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AA509" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO509" t="inlineStr">

--- a/countries/br-ac/2000-2004.xlsx
+++ b/countries/br-ac/2000-2004.xlsx
@@ -1702,7 +1702,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -2792,7 +2792,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -5292,7 +5292,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
@@ -6382,7 +6382,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -7472,7 +7472,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -11100,7 +11100,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -13459,7 +13459,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -16100,7 +16100,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -18741,7 +18741,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -20254,7 +20254,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -24023,7 +24023,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -27792,7 +27792,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">
@@ -29305,7 +29305,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -34202,7 +34202,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
@@ -42483,7 +42483,7 @@
       </c>
       <c r="AJ287" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK287" t="inlineStr">
@@ -49636,7 +49636,7 @@
       </c>
       <c r="AJ337" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK337" t="inlineStr">
@@ -54533,7 +54533,7 @@
       </c>
       <c r="AJ371" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK371" t="inlineStr">
@@ -59712,7 +59712,7 @@
       </c>
       <c r="AJ407" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK407" t="inlineStr">
@@ -61366,7 +61366,7 @@
       </c>
       <c r="AJ418" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK418" t="inlineStr">
@@ -63020,7 +63020,7 @@
       </c>
       <c r="AJ429" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK429" t="inlineStr">
@@ -64674,7 +64674,7 @@
       </c>
       <c r="AJ440" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK440" t="inlineStr">
@@ -67597,7 +67597,7 @@
       </c>
       <c r="AJ460" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK460" t="inlineStr">
@@ -70520,7 +70520,7 @@
       </c>
       <c r="AJ480" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK480" t="inlineStr">
@@ -73443,7 +73443,7 @@
       </c>
       <c r="AJ500" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK500" t="inlineStr">
